--- a/data/trans_bre/P19C05-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P19C05-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,74; 5,4</t>
+          <t>-6,13; 5,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,45; 0,84</t>
+          <t>-8,28; 1,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 6,42</t>
+          <t>-2,8; 6,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 1,93</t>
+          <t>-3,95; 1,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-36,96; 47,93</t>
+          <t>-38,21; 46,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-62,37; 11,21</t>
+          <t>-60,13; 13,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-30,56; 119,42</t>
+          <t>-29,86; 112,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-40,01; 31,26</t>
+          <t>-38,28; 29,25</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-10,41; -0,42</t>
+          <t>-10,34; -0,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-13,08; -3,01</t>
+          <t>-12,9; -2,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,01; 0,52</t>
+          <t>-8,53; 0,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,14; -0,87</t>
+          <t>-8,31; -0,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-64,77; -2,76</t>
+          <t>-64,96; -5,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-68,88; -21,23</t>
+          <t>-67,7; -18,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-64,17; 7,92</t>
+          <t>-65,79; 9,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-58,52; -8,55</t>
+          <t>-61,42; -9,89</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,3; 3,92</t>
+          <t>-8,03; 2,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,3; 14,33</t>
+          <t>0,89; 14,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 8,39</t>
+          <t>-6,81; 9,03</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,76; 16,54</t>
+          <t>2,08; 16,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-58,27; 37,83</t>
+          <t>-57,64; 28,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,39; 108,92</t>
+          <t>4,78; 107,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-40,22; 60,21</t>
+          <t>-39,79; 64,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,32; 542,31</t>
+          <t>17,04; 496,34</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,12; -0,33</t>
+          <t>-7,96; -0,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 0,35</t>
+          <t>-6,74; 0,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,29; -1,31</t>
+          <t>-7,39; -1,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,37; -2,09</t>
+          <t>-9,61; -1,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-41,31; -1,97</t>
+          <t>-40,73; -0,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-36,86; 2,19</t>
+          <t>-36,81; 6,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-53,24; -9,16</t>
+          <t>-53,65; -11,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-70,51; -18,0</t>
+          <t>-70,13; -16,95</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 9,95</t>
+          <t>-0,75; 10,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,51; 11,3</t>
+          <t>0,31; 11,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 8,08</t>
+          <t>-0,46; 8,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 7,49</t>
+          <t>-0,1; 7,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 122,3</t>
+          <t>-6,57; 121,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,34; 71,67</t>
+          <t>1,25; 71,3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,08; 101,86</t>
+          <t>-3,77; 105,6</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,73; 107,39</t>
+          <t>-0,05; 103,42</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17,87; 24,04</t>
+          <t>17,92; 24,15</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14,56; 22,43</t>
+          <t>14,56; 22,41</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,41; 14,42</t>
+          <t>7,63; 14,9</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10,61; 17,55</t>
+          <t>10,55; 17,39</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>511,41; 5451,5</t>
+          <t>505,11; 5556,01</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>218,9; 1201,63</t>
+          <t>201,13; 1100,25</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>96,47; 680,03</t>
+          <t>109,12; 697,05</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>169,64; 2573,14</t>
+          <t>159,44; 2333,12</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,56; 4,46</t>
+          <t>0,61; 4,6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,41; 5,09</t>
+          <t>1,19; 5,26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 2,63</t>
+          <t>-0,81; 2,56</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 3,82</t>
+          <t>-0,63; 3,85</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,37; 35,49</t>
+          <t>4,3; 37,12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,7; 36,56</t>
+          <t>7,39; 37,58</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 26,76</t>
+          <t>-7,07; 25,91</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 44,75</t>
+          <t>-5,64; 48,9</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P19C05-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P19C05-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1,03</t>
+          <t>-1,33</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-12,35%</t>
+          <t>-15,65%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,13; 5,29</t>
+          <t>-5,91; 5,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 1,04</t>
+          <t>-8,66; 1,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 6,26</t>
+          <t>-2,18; 6,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 1,81</t>
+          <t>-4,17; 1,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-38,21; 46,78</t>
+          <t>-37,61; 44,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-60,13; 13,91</t>
+          <t>-60,84; 16,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-29,86; 112,58</t>
+          <t>-26,13; 114,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-38,28; 29,25</t>
+          <t>-40,95; 22,15</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-4,53</t>
+          <t>-4,52</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-39,12%</t>
+          <t>-39,41%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-10,34; -0,73</t>
+          <t>-9,68; -0,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-12,9; -2,68</t>
+          <t>-13,87; -2,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,53; 0,47</t>
+          <t>-8,71; 0,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,31; -0,99</t>
+          <t>-7,94; -0,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-64,96; -5,29</t>
+          <t>-62,77; -1,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-67,7; -18,4</t>
+          <t>-69,98; -19,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-65,79; 9,11</t>
+          <t>-65,92; 14,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-61,42; -9,89</t>
+          <t>-59,48; -10,75</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8,16</t>
+          <t>3,96</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>105,01%</t>
+          <t>32,88%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,03; 2,97</t>
+          <t>-8,72; 3,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 14,66</t>
+          <t>0,77; 14,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,81; 9,03</t>
+          <t>-6,61; 9,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,08; 16,18</t>
+          <t>-0,94; 9,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-57,64; 28,06</t>
+          <t>-61,83; 33,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,78; 107,79</t>
+          <t>2,21; 106,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-39,79; 64,65</t>
+          <t>-38,89; 67,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,04; 496,34</t>
+          <t>-7,63; 96,2</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-5,1</t>
+          <t>-3,65</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-40,66%</t>
+          <t>-28,19%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,96; -0,16</t>
+          <t>-7,85; -0,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 0,87</t>
+          <t>-6,6; 0,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,39; -1,33</t>
+          <t>-7,6; -1,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,61; -1,96</t>
+          <t>-6,2; -1,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-40,73; -0,9</t>
+          <t>-40,1; -0,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-36,81; 6,59</t>
+          <t>-36,55; 2,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-53,65; -11,9</t>
+          <t>-55,61; -11,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-70,13; -16,95</t>
+          <t>-42,89; -11,01</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,16</t>
+          <t>6,68</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>83,38%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 10,17</t>
+          <t>-0,5; 10,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,31; 11,09</t>
+          <t>0,54; 11,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 8,28</t>
+          <t>-0,26; 8,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 7,59</t>
+          <t>3,69; 9,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 121,86</t>
+          <t>-4,98; 129,59</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,25; 71,3</t>
+          <t>2,62; 72,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 105,6</t>
+          <t>-2,49; 103,82</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 103,42</t>
+          <t>37,04; 152,86</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14,61</t>
+          <t>14,39</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>623,93%</t>
+          <t>566,71%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17,92; 24,15</t>
+          <t>17,66; 24,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14,56; 22,41</t>
+          <t>14,45; 22,23</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,63; 14,9</t>
+          <t>7,44; 14,72</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10,55; 17,39</t>
+          <t>10,24; 17,34</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>505,11; 5556,01</t>
+          <t>505,46; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>201,13; 1100,25</t>
+          <t>218,52; 1181,11</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>109,12; 697,05</t>
+          <t>92,31; 658,94</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>159,44; 2333,12</t>
+          <t>141,83; 2231,86</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1,51</t>
+          <t>1,65</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,81%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,61; 4,6</t>
+          <t>0,47; 4,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,19; 5,26</t>
+          <t>1,12; 5,14</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 2,56</t>
+          <t>-0,79; 2,68</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 3,85</t>
+          <t>0,24; 3,01</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,3; 37,12</t>
+          <t>3,14; 34,8</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,39; 37,58</t>
+          <t>6,93; 37,24</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 25,91</t>
+          <t>-6,85; 27,73</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 48,9</t>
+          <t>1,87; 30,9</t>
         </is>
       </c>
     </row>
